--- a/mii-cm-onko-allgemeiner-leistungszustand-sct.xlsx
+++ b/mii-cm-onko-allgemeiner-leistungszustand-sct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>

--- a/mii-cm-onko-allgemeiner-leistungszustand-sct.xlsx
+++ b/mii-cm-onko-allgemeiner-leistungszustand-sct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
